--- a/data/carriers_data/biomass/biomass_availability.xlsx
+++ b/data/carriers_data/biomass/biomass_availability.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\carriers_data\biomass\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92081E9A-4958-4D7D-B9B5-7F70F4E006F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E192445-8CF3-45FB-AC73-7B681C0285B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/carriers_data/biomass/biomass_availability.xlsx
+++ b/data/carriers_data/biomass/biomass_availability.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E192445-8CF3-45FB-AC73-7B681C0285B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>

--- a/data/carriers_data/biomass/biomass_availability.xlsx
+++ b/data/carriers_data/biomass/biomass_availability.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E192445-8CF3-45FB-AC73-7B681C0285B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E016A24-6158-41A8-92C8-4EE25F4FAF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16620" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>
@@ -18,10 +18,21 @@
     <sheet name="ENS_Med" sheetId="2" r:id="rId3"/>
     <sheet name="ENS_High" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -366,9 +377,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA827D2A-3E24-48EA-BA45-22F19B96F0CC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -381,9 +392,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -397,54 +408,62 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>8.0103419999999996</v>
+        <f>8.010342+4</f>
+        <v>12.010342</v>
       </c>
       <c r="C2" s="1">
-        <v>5.3409829999999996</v>
+        <f>5.340983+2.7</f>
+        <v>8.0409830000000007</v>
       </c>
       <c r="D2" s="1">
-        <v>5.341526</v>
+        <f>5.341526+2.7</f>
+        <v>8.0415260000000011</v>
       </c>
       <c r="E2" s="1">
-        <v>2.6708769999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <f>2.670877+1.3</f>
+        <v>3.9708769999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D3">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E3">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>0.233156</v>
+        <f>0.233156+0.1</f>
+        <v>0.33315600000000001</v>
       </c>
       <c r="C4" s="1">
-        <v>0.29725099999999999</v>
+        <f>0.297251+0.1</f>
+        <v>0.39725100000000002</v>
       </c>
       <c r="D4" s="1">
-        <v>0.29725099999999999</v>
+        <f>0.297251+0.1</f>
+        <v>0.39725100000000002</v>
       </c>
       <c r="E4" s="1">
+        <f>0.148625+0</f>
         <v>0.14862500000000001</v>
       </c>
     </row>
@@ -456,9 +475,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD98E45F-EEB3-4F00-B435-84ED2BD9104F}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -472,55 +491,63 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>13.350569999999999</v>
+        <f>13.35057+6.6</f>
+        <v>19.950569999999999</v>
       </c>
       <c r="C2" s="1">
-        <v>10.68197</v>
+        <f>10.68197+5.3</f>
+        <v>15.98197</v>
       </c>
       <c r="D2" s="1">
-        <v>10.68305</v>
+        <f>10.68305+5.3</f>
+        <v>15.983049999999999</v>
       </c>
       <c r="E2" s="1">
-        <v>10.68305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <f>10.68305+5.3</f>
+        <v>15.983049999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>0.38859300000000002</v>
+        <f>0.388593+0.2</f>
+        <v>0.58859300000000003</v>
       </c>
       <c r="C4" s="1">
-        <v>0.59450199999999997</v>
+        <f>0.594502+0.2</f>
+        <v>0.79450200000000004</v>
       </c>
       <c r="D4" s="1">
-        <v>0.59450199999999997</v>
+        <f>0.594502+0.2</f>
+        <v>0.79450200000000004</v>
       </c>
       <c r="E4" s="1">
-        <v>0.59450199999999997</v>
+        <f>0.594502+0.2</f>
+        <v>0.79450200000000004</v>
       </c>
     </row>
   </sheetData>
@@ -531,9 +558,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F625CA6D-F24C-4084-A44C-75DED3A76FF6}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -547,55 +574,63 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>26.701139999999999</v>
+        <f>26.70114+13.3</f>
+        <v>40.001139999999999</v>
       </c>
       <c r="C2" s="1">
-        <v>26.704910000000002</v>
+        <f>26.70491+13.3</f>
+        <v>40.004910000000002</v>
       </c>
       <c r="D2" s="1">
-        <v>26.707630000000002</v>
+        <f>26.70763+13.3</f>
+        <v>40.007630000000006</v>
       </c>
       <c r="E2" s="1">
-        <v>26.708770000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <f>26.70877+13.3</f>
+        <v>40.008769999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.3000000000000007</v>
+        <v>10.5</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>13.1</v>
       </c>
       <c r="D3">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="E3">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1">
-        <v>0.77718600000000004</v>
+        <f>0.777186+0.4</f>
+        <v>1.1771860000000001</v>
       </c>
       <c r="C4" s="1">
-        <v>1.486254</v>
+        <f>1.486254+0.4</f>
+        <v>1.8862540000000001</v>
       </c>
       <c r="D4" s="1">
-        <v>1.486254</v>
+        <f>1.486254+0.4</f>
+        <v>1.8862540000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>1.486254</v>
+        <f>1.486254+0.4</f>
+        <v>1.8862540000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/carriers_data/biomass/biomass_availability.xlsx
+++ b/data/carriers_data/biomass/biomass_availability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E016A24-6158-41A8-92C8-4EE25F4FAF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D22CA-BB0C-466D-94FF-9F5CC1D43DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16620" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>

--- a/data/carriers_data/biomass/biomass_availability.xlsx
+++ b/data/carriers_data/biomass/biomass_availability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D22CA-BB0C-466D-94FF-9F5CC1D43DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCEEDF2-60D0-417B-A932-0E110E15F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="-14100" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>
@@ -50,7 +50,7 @@
     <t>DE</t>
   </si>
   <si>
-    <t>Availability is expressed in PJ</t>
+    <t>Availability is expressed in PJ/y</t>
   </si>
 </sst>
 </file>
